--- a/public/templates/invigilation-template.xlsx
+++ b/public/templates/invigilation-template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\我的雲端硬碟\AI_Agent\100_Todo\projects\vibe-coding\school-substitution-sys\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\我的雲端硬碟\AI_Agent\100_Todo\projects\vibe-coding\school-substitution-sys\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBD56792-04D2-4F52-9EEC-35D598CB4400}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F81D86C-A5A8-4AB9-9F55-1460343F4E54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2D53BEDC-658E-4916-BAED-16A4B4875AEA}"/>
   </bookViews>
@@ -145,7 +145,7 @@
 (2)各科考試時間皆為一節課(45分鐘)，測驗開始及結束時間皆以學校鐘聲為準。
 (3)監考表原則採隨班監考方式安排呈現，部分節次因命題巡堂與考科當節迴避而適度調整，請留意監考節次與班級。 
 (4)請老師專心監考，不要讓學生有作弊的機會，並請於非考試節次依本表準時入班監看自習。
-(5)校外教學期間，教師未執行課務(安排已劃底線註記)，依節次安排於本學年段考監考、監看自習或代理遺留課程【未執行的課務共_____節，本次段考已安排_____節，尚有____節，未執行節數將會累計於本學年度】</t>
+(5)校外教學期間，教師未執行課務(安排已劃底線註記)，依節數安排於本學年段考監考、監看自習或代理遺留課程【未執行的課務共_____節，本次段考已安排_____節，尚有____節，未執行節數將會累計於本學年度】</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
